--- a/public/templates/template_base_dados_analises_diario_categorias_simplificadas.xlsx
+++ b/public/templates/template_base_dados_analises_diario_categorias_simplificadas.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomarcadores" sheetId="1" r:id="R8e9fedb0ad964f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analises" sheetId="2" r:id="Rfe5afaa6384546c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comportamentos" sheetId="3" r:id="R10e7153747ab4c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario_Comportamentos" sheetId="4" r:id="R72ae2136d9624f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto" sheetId="5" r:id="Ra6cd1810165d41ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomarcadores" sheetId="1" r:id="R22f4589575584817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analises" sheetId="2" r:id="R4e5ccd879ab34ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comportamentos" sheetId="3" r:id="Rdd3f6bbe69434ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario_Comportamentos" sheetId="4" r:id="Rd144c1e8dfae4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto" sheetId="5" r:id="Rc9ed6363b91945c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1010,10 +1010,12 @@
       <x:c r="E22" s="8" t="str">
         <x:v>Ureia depois da sessão de diálise.</x:v>
       </x:c>
-      <x:c r="F22" s="8" t="str"/>
-      <x:c r="G22" s="8" t="str"/>
-      <x:c r="H22" s="8" t="str"/>
-      <x:c r="I22" s="8" t="str"/>
+      <x:c r="F22" s="8"/>
+      <x:c r="G22" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H22" s="8"/>
+      <x:c r="I22" s="8"/>
       <x:c r="J22" s="8" t="str">
         <x:v>menor</x:v>
       </x:c>
@@ -3879,7 +3881,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c47d78bab7f46d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29e0f76113da4488"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6559,7 +6561,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a485169ea3a4530"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0571d827ca2a4fdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8195,7 +8197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1888074fedf34f08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R564e84a733fc49a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10696,7 +10698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe34b8e3e104259"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R036c70f8d2ea4262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12742,7 +12744,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa405ddd875432d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06a412657f274cc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>